--- a/data/RESULTADOS.xlsx
+++ b/data/RESULTADOS.xlsx
@@ -4,10 +4,10 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648"/>
   </bookViews>
   <sheets>
-    <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="resultados" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -16,6 +16,38 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="9">
+  <si>
+    <t>fecha</t>
+  </si>
+  <si>
+    <t>equipo_local</t>
+  </si>
+  <si>
+    <t>puntos_local</t>
+  </si>
+  <si>
+    <t>equipo_visitante</t>
+  </si>
+  <si>
+    <t>puntos_visitante</t>
+  </si>
+  <si>
+    <t>Tigres</t>
+  </si>
+  <si>
+    <t>Leones</t>
+  </si>
+  <si>
+    <t>Tiburones</t>
+  </si>
+  <si>
+    <t>Condores</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -49,8 +81,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -69,7 +102,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -114,7 +147,7 @@
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic Light"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
@@ -149,7 +182,7 @@
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Yu Gothic"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
@@ -331,9 +364,202 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="14.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="1">
+        <v>46174</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2">
+        <v>78</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="1">
+        <v>46175</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3">
+        <v>82</v>
+      </c>
+      <c r="D3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
+        <v>46176</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4">
+        <v>70</v>
+      </c>
+      <c r="D4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="1">
+        <v>46177</v>
+      </c>
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5">
+        <v>90</v>
+      </c>
+      <c r="D5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
+        <v>46178</v>
+      </c>
+      <c r="B6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>95</v>
+      </c>
+      <c r="D6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="1">
+        <v>46179</v>
+      </c>
+      <c r="B7" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <v>84</v>
+      </c>
+      <c r="D7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="1">
+        <v>46180</v>
+      </c>
+      <c r="B8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8">
+        <v>77</v>
+      </c>
+      <c r="D8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
+        <v>46181</v>
+      </c>
+      <c r="B9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9">
+        <v>85</v>
+      </c>
+      <c r="D9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
+        <v>46182</v>
+      </c>
+      <c r="B10" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10">
+        <v>80</v>
+      </c>
+      <c r="D10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11">
+        <v>68</v>
+      </c>
+      <c r="D11" t="s">
+        <v>5</v>
+      </c>
+      <c r="E11">
+        <v>74</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/RESULTADOS.xlsx
+++ b/data/RESULTADOS.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="15">
   <si>
     <t>fecha</t>
   </si>
@@ -46,6 +46,24 @@
   </si>
   <si>
     <t>Condores</t>
+  </si>
+  <si>
+    <t>Pumas</t>
+  </si>
+  <si>
+    <t>Halcones</t>
+  </si>
+  <si>
+    <t>estado</t>
+  </si>
+  <si>
+    <t>NO_PRESENTA_VISITA</t>
+  </si>
+  <si>
+    <t>NORMAL</t>
+  </si>
+  <si>
+    <t>NO_PRESENTA_LOCAL</t>
   </si>
 </sst>
 </file>
@@ -364,7 +382,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
@@ -372,7 +390,7 @@
     <col min="4" max="5" width="14.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -388,8 +406,11 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>46174</v>
       </c>
@@ -405,8 +426,11 @@
       <c r="E2">
         <v>65</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>46175</v>
       </c>
@@ -422,8 +446,11 @@
       <c r="E3">
         <v>80</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>46176</v>
       </c>
@@ -439,8 +466,11 @@
       <c r="E4">
         <v>75</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>46177</v>
       </c>
@@ -456,8 +486,11 @@
       <c r="E5">
         <v>88</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>46178</v>
       </c>
@@ -473,8 +506,11 @@
       <c r="E6">
         <v>89</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>46179</v>
       </c>
@@ -482,16 +518,19 @@
         <v>6</v>
       </c>
       <c r="C7">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="D7" t="s">
         <v>7</v>
       </c>
       <c r="E7">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+      <c r="F7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>46180</v>
       </c>
@@ -507,8 +546,11 @@
       <c r="E8">
         <v>72</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>46181</v>
       </c>
@@ -524,8 +566,11 @@
       <c r="E9">
         <v>91</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>46182</v>
       </c>
@@ -541,8 +586,11 @@
       <c r="E10">
         <v>76</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>46183</v>
       </c>
@@ -557,6 +605,49 @@
       </c>
       <c r="E11">
         <v>74</v>
+      </c>
+      <c r="F11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="1">
+        <v>46184</v>
+      </c>
+      <c r="B12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12">
+        <v>10</v>
+      </c>
+      <c r="D12" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12">
+        <v>50</v>
+      </c>
+      <c r="F12" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="1">
+        <v>46184</v>
+      </c>
+      <c r="B13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13">
+        <v>20</v>
+      </c>
+      <c r="D13" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
